--- a/策划/excel/16_RelmEvent.xlsx
+++ b/策划/excel/16_RelmEvent.xlsx
@@ -9,10 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27765" windowHeight="9540"/>
+    <workbookView windowWidth="27315" windowHeight="10470"/>
   </bookViews>
   <sheets>
-    <sheet name="11_Realms" sheetId="1" r:id="rId1"/>
+    <sheet name="16_RelmEvent" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="130">
   <si>
     <t>编号【KEY】</t>
   </si>
   <si>
-    <t>世界</t>
+    <t>世界ID</t>
   </si>
   <si>
     <t>世界名字</t>
@@ -94,13 +94,334 @@
     <t>阿斯加德</t>
   </si>
   <si>
+    <t>[150091]</t>
+  </si>
+  <si>
+    <t>[140001]</t>
+  </si>
+  <si>
+    <t>[60002,60001]</t>
+  </si>
+  <si>
+    <t>[150092]</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>[6001]</t>
-  </si>
-  <si>
-    <t>[6001,6002]</t>
+    <t>[60002]</t>
+  </si>
+  <si>
+    <t>[150093]</t>
+  </si>
+  <si>
+    <t>[150094]</t>
+  </si>
+  <si>
+    <t>[150095]</t>
+  </si>
+  <si>
+    <t>[150096]</t>
+  </si>
+  <si>
+    <t>[150097]</t>
+  </si>
+  <si>
+    <t>[150098]</t>
+  </si>
+  <si>
+    <t>[150099]</t>
+  </si>
+  <si>
+    <t>[150100]</t>
+  </si>
+  <si>
+    <t>米德加德</t>
+  </si>
+  <si>
+    <t>[150011]</t>
+  </si>
+  <si>
+    <t>[150012]</t>
+  </si>
+  <si>
+    <t>[150013]</t>
+  </si>
+  <si>
+    <t>[140002,140010]</t>
+  </si>
+  <si>
+    <t>[150014]</t>
+  </si>
+  <si>
+    <t>[150015]</t>
+  </si>
+  <si>
+    <t>[150016]</t>
+  </si>
+  <si>
+    <t>[150017]</t>
+  </si>
+  <si>
+    <t>[150018]</t>
+  </si>
+  <si>
+    <t>[150019]</t>
+  </si>
+  <si>
+    <t>[150020]</t>
+  </si>
+  <si>
+    <t>华纳海姆</t>
+  </si>
+  <si>
+    <t>[150021]</t>
+  </si>
+  <si>
+    <t>[150022]</t>
+  </si>
+  <si>
+    <t>[150023]</t>
+  </si>
+  <si>
+    <t>[140003]</t>
+  </si>
+  <si>
+    <t>[150024]</t>
+  </si>
+  <si>
+    <t>[150025]</t>
+  </si>
+  <si>
+    <t>[150026]</t>
+  </si>
+  <si>
+    <t>[150027]</t>
+  </si>
+  <si>
+    <t>[150028]</t>
+  </si>
+  <si>
+    <t>[150029]</t>
+  </si>
+  <si>
+    <t>[150030]</t>
+  </si>
+  <si>
+    <t>亚尔夫海姆</t>
+  </si>
+  <si>
+    <t>[150031]</t>
+  </si>
+  <si>
+    <t>[150032]</t>
+  </si>
+  <si>
+    <t>[150033]</t>
+  </si>
+  <si>
+    <t>[140004]</t>
+  </si>
+  <si>
+    <t>[150034]</t>
+  </si>
+  <si>
+    <t>[150035]</t>
+  </si>
+  <si>
+    <t>[150036]</t>
+  </si>
+  <si>
+    <t>[150037]</t>
+  </si>
+  <si>
+    <t>[150038]</t>
+  </si>
+  <si>
+    <t>[150039]</t>
+  </si>
+  <si>
+    <t>[150040]</t>
+  </si>
+  <si>
+    <t>约顿海姆</t>
+  </si>
+  <si>
+    <t>[150041]</t>
+  </si>
+  <si>
+    <t>[150042]</t>
+  </si>
+  <si>
+    <t>[150043]</t>
+  </si>
+  <si>
+    <t>[140005]</t>
+  </si>
+  <si>
+    <t>[150044]</t>
+  </si>
+  <si>
+    <t>[150045]</t>
+  </si>
+  <si>
+    <t>[150046]</t>
+  </si>
+  <si>
+    <t>[150047]</t>
+  </si>
+  <si>
+    <t>[150048]</t>
+  </si>
+  <si>
+    <t>[150049]</t>
+  </si>
+  <si>
+    <t>[150050]</t>
+  </si>
+  <si>
+    <t>尼达维勒</t>
+  </si>
+  <si>
+    <t>[150051]</t>
+  </si>
+  <si>
+    <t>[150052]</t>
+  </si>
+  <si>
+    <t>[150053]</t>
+  </si>
+  <si>
+    <t>[140006]</t>
+  </si>
+  <si>
+    <t>[150054]</t>
+  </si>
+  <si>
+    <t>[150055]</t>
+  </si>
+  <si>
+    <t>[150056]</t>
+  </si>
+  <si>
+    <t>[150057]</t>
+  </si>
+  <si>
+    <t>[150058]</t>
+  </si>
+  <si>
+    <t>[150059]</t>
+  </si>
+  <si>
+    <t>[150060]</t>
+  </si>
+  <si>
+    <t>尼福尔海姆</t>
+  </si>
+  <si>
+    <t>[150061]</t>
+  </si>
+  <si>
+    <t>[150062]</t>
+  </si>
+  <si>
+    <t>[150063]</t>
+  </si>
+  <si>
+    <t>[140007]</t>
+  </si>
+  <si>
+    <t>[150064]</t>
+  </si>
+  <si>
+    <t>[150065]</t>
+  </si>
+  <si>
+    <t>[150066]</t>
+  </si>
+  <si>
+    <t>[150067]</t>
+  </si>
+  <si>
+    <t>[150068]</t>
+  </si>
+  <si>
+    <t>[150069]</t>
+  </si>
+  <si>
+    <t>[150070]</t>
+  </si>
+  <si>
+    <t>穆斯贝尔海姆</t>
+  </si>
+  <si>
+    <t>[150071]</t>
+  </si>
+  <si>
+    <t>[150072]</t>
+  </si>
+  <si>
+    <t>[150073]</t>
+  </si>
+  <si>
+    <t>[140008]</t>
+  </si>
+  <si>
+    <t>[150074]</t>
+  </si>
+  <si>
+    <t>[150075]</t>
+  </si>
+  <si>
+    <t>[150076]</t>
+  </si>
+  <si>
+    <t>[150077]</t>
+  </si>
+  <si>
+    <t>[150078]</t>
+  </si>
+  <si>
+    <t>[150079]</t>
+  </si>
+  <si>
+    <t>[150080]</t>
+  </si>
+  <si>
+    <t>赫尔海姆</t>
+  </si>
+  <si>
+    <t>[150081]</t>
+  </si>
+  <si>
+    <t>[150082]</t>
+  </si>
+  <si>
+    <t>[150083]</t>
+  </si>
+  <si>
+    <t>[140009]</t>
+  </si>
+  <si>
+    <t>[150084]</t>
+  </si>
+  <si>
+    <t>[150085]</t>
+  </si>
+  <si>
+    <t>[150086]</t>
+  </si>
+  <si>
+    <t>[150087]</t>
+  </si>
+  <si>
+    <t>[150088]</t>
+  </si>
+  <si>
+    <t>[150089]</t>
+  </si>
+  <si>
+    <t>[150090]</t>
   </si>
 </sst>
 </file>
@@ -113,7 +434,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,11 +445,6 @@
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -594,142 +910,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -986,14 +1301,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.752380952381" customWidth="1"/>
     <col min="2" max="2" width="25.1238095238095" customWidth="1"/>
     <col min="3" max="4" width="13.247619047619" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="7" width="13.247619047619" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="13.247619047619" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:7">
@@ -1047,7 +1363,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
@@ -1118,7 +1434,7 @@
       <c r="B6">
         <v>110001</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6">
@@ -1128,10 +1444,10 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7">
@@ -1139,22 +1455,22 @@
         <v>160002</v>
       </c>
       <c r="B7">
-        <v>110002</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7">
@@ -1162,19 +1478,22 @@
         <v>160003</v>
       </c>
       <c r="B8">
-        <v>110003</v>
-      </c>
-      <c r="C8" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7">
@@ -1182,19 +1501,22 @@
         <v>160004</v>
       </c>
       <c r="B9">
-        <v>110004</v>
-      </c>
-      <c r="C9" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7">
@@ -1202,19 +1524,22 @@
         <v>160005</v>
       </c>
       <c r="B10">
-        <v>110005</v>
-      </c>
-      <c r="C10" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7">
@@ -1222,19 +1547,22 @@
         <v>160006</v>
       </c>
       <c r="B11">
-        <v>110006</v>
-      </c>
-      <c r="C11" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7">
@@ -1242,19 +1570,22 @@
         <v>160007</v>
       </c>
       <c r="B12">
-        <v>110007</v>
-      </c>
-      <c r="C12" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12">
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7">
@@ -1262,19 +1593,22 @@
         <v>160008</v>
       </c>
       <c r="B13">
-        <v>110008</v>
-      </c>
-      <c r="C13" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:7">
@@ -1282,39 +1616,1885 @@
         <v>160009</v>
       </c>
       <c r="B14">
-        <v>110009</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:7">
       <c r="A15">
         <v>160010</v>
       </c>
       <c r="B15">
-        <v>110010</v>
-      </c>
-      <c r="C15" s="2" t="s">
+        <v>110001</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:7">
+      <c r="A16">
+        <v>160011</v>
+      </c>
+      <c r="B16">
+        <v>110002</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:7">
+      <c r="A17">
+        <v>160012</v>
+      </c>
+      <c r="B17">
+        <v>110002</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:7">
+      <c r="A18">
+        <v>160013</v>
+      </c>
+      <c r="B18">
+        <v>110002</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:7">
+      <c r="A19">
+        <v>160014</v>
+      </c>
+      <c r="B19">
+        <v>110002</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:7">
+      <c r="A20">
+        <v>160015</v>
+      </c>
+      <c r="B20">
+        <v>110002</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:7">
+      <c r="A21">
+        <v>160016</v>
+      </c>
+      <c r="B21">
+        <v>110002</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:7">
+      <c r="A22">
+        <v>160017</v>
+      </c>
+      <c r="B22">
+        <v>110002</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:7">
+      <c r="A23">
+        <v>160018</v>
+      </c>
+      <c r="B23">
+        <v>110002</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:7">
+      <c r="A24">
+        <v>160019</v>
+      </c>
+      <c r="B24">
+        <v>110002</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:7">
+      <c r="A25">
+        <v>160020</v>
+      </c>
+      <c r="B25">
+        <v>110002</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:7">
+      <c r="A26">
+        <v>160021</v>
+      </c>
+      <c r="B26">
+        <v>110003</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:7">
+      <c r="A27">
+        <v>160022</v>
+      </c>
+      <c r="B27">
+        <v>110003</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:7">
+      <c r="A28">
+        <v>160023</v>
+      </c>
+      <c r="B28">
+        <v>110003</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:7">
+      <c r="A29">
+        <v>160024</v>
+      </c>
+      <c r="B29">
+        <v>110003</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:7">
+      <c r="A30">
+        <v>160025</v>
+      </c>
+      <c r="B30">
+        <v>110003</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:7">
+      <c r="A31">
+        <v>160026</v>
+      </c>
+      <c r="B31">
+        <v>110003</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:7">
+      <c r="A32">
+        <v>160027</v>
+      </c>
+      <c r="B32">
+        <v>110003</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:7">
+      <c r="A33">
+        <v>160028</v>
+      </c>
+      <c r="B33">
+        <v>110003</v>
+      </c>
+      <c r="C33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:7">
+      <c r="A34">
+        <v>160029</v>
+      </c>
+      <c r="B34">
+        <v>110003</v>
+      </c>
+      <c r="C34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:7">
+      <c r="A35">
+        <v>160030</v>
+      </c>
+      <c r="B35">
+        <v>110003</v>
+      </c>
+      <c r="C35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:7">
+      <c r="A36">
+        <v>160031</v>
+      </c>
+      <c r="B36">
+        <v>110004</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:7">
+      <c r="A37">
+        <v>160032</v>
+      </c>
+      <c r="B37">
+        <v>110004</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:7">
+      <c r="A38">
+        <v>160033</v>
+      </c>
+      <c r="B38">
+        <v>110004</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:7">
+      <c r="A39">
+        <v>160034</v>
+      </c>
+      <c r="B39">
+        <v>110004</v>
+      </c>
+      <c r="C39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:7">
+      <c r="A40">
+        <v>160035</v>
+      </c>
+      <c r="B40">
+        <v>110004</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:7">
+      <c r="A41">
+        <v>160036</v>
+      </c>
+      <c r="B41">
+        <v>110004</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:7">
+      <c r="A42">
+        <v>160037</v>
+      </c>
+      <c r="B42">
+        <v>110004</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F42" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:7">
+      <c r="A43">
+        <v>160038</v>
+      </c>
+      <c r="B43">
+        <v>110004</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:7">
+      <c r="A44">
+        <v>160039</v>
+      </c>
+      <c r="B44">
+        <v>110004</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:7">
+      <c r="A45">
+        <v>160040</v>
+      </c>
+      <c r="B45">
+        <v>110004</v>
+      </c>
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:7">
+      <c r="A46">
+        <v>160041</v>
+      </c>
+      <c r="B46">
+        <v>110005</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:7">
+      <c r="A47">
+        <v>160042</v>
+      </c>
+      <c r="B47">
+        <v>110005</v>
+      </c>
+      <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:7">
+      <c r="A48">
+        <v>160043</v>
+      </c>
+      <c r="B48">
+        <v>110005</v>
+      </c>
+      <c r="C48" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" t="s">
+        <v>74</v>
+      </c>
+      <c r="G48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:7">
+      <c r="A49">
+        <v>160044</v>
+      </c>
+      <c r="B49">
+        <v>110005</v>
+      </c>
+      <c r="C49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="1:7">
+      <c r="A50">
+        <v>160045</v>
+      </c>
+      <c r="B50">
+        <v>110005</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="1:7">
+      <c r="A51">
+        <v>160046</v>
+      </c>
+      <c r="B51">
+        <v>110005</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+      <c r="E51" t="s">
+        <v>77</v>
+      </c>
+      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="G51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:7">
+      <c r="A52">
+        <v>160047</v>
+      </c>
+      <c r="B52">
+        <v>110005</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="1:7">
+      <c r="A53">
+        <v>160048</v>
+      </c>
+      <c r="B53">
+        <v>110005</v>
+      </c>
+      <c r="C53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="1:7">
+      <c r="A54">
+        <v>160049</v>
+      </c>
+      <c r="B54">
+        <v>110005</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:7">
+      <c r="A55">
+        <v>160050</v>
+      </c>
+      <c r="B55">
+        <v>110005</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="1:7">
+      <c r="A56">
+        <v>160051</v>
+      </c>
+      <c r="B56">
+        <v>110006</v>
+      </c>
+      <c r="C56" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" ht="15" spans="1:7">
+      <c r="A57">
+        <v>160052</v>
+      </c>
+      <c r="B57">
+        <v>110006</v>
+      </c>
+      <c r="C57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:7">
+      <c r="A58">
+        <v>160053</v>
+      </c>
+      <c r="B58">
+        <v>110006</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" t="s">
+        <v>86</v>
+      </c>
+      <c r="G58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:7">
+      <c r="A59">
+        <v>160054</v>
+      </c>
+      <c r="B59">
+        <v>110006</v>
+      </c>
+      <c r="C59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>87</v>
+      </c>
+      <c r="F59" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" ht="15" spans="1:7">
+      <c r="A60">
+        <v>160055</v>
+      </c>
+      <c r="B60">
+        <v>110006</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" ht="15" spans="1:7">
+      <c r="A61">
+        <v>160056</v>
+      </c>
+      <c r="B61">
+        <v>110006</v>
+      </c>
+      <c r="C61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" t="s">
+        <v>86</v>
+      </c>
+      <c r="G61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:7">
+      <c r="A62">
+        <v>160057</v>
+      </c>
+      <c r="B62">
+        <v>110006</v>
+      </c>
+      <c r="C62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" ht="15" spans="1:7">
+      <c r="A63">
+        <v>160058</v>
+      </c>
+      <c r="B63">
+        <v>110006</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>91</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:7">
+      <c r="A64">
+        <v>160059</v>
+      </c>
+      <c r="B64">
+        <v>110006</v>
+      </c>
+      <c r="C64" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>92</v>
+      </c>
+      <c r="F64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" ht="15" spans="1:7">
+      <c r="A65">
+        <v>160060</v>
+      </c>
+      <c r="B65">
+        <v>110006</v>
+      </c>
+      <c r="C65" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" ht="15" spans="1:7">
+      <c r="A66">
+        <v>160061</v>
+      </c>
+      <c r="B66">
+        <v>110007</v>
+      </c>
+      <c r="C66" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>95</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:7">
+      <c r="A67">
+        <v>160062</v>
+      </c>
+      <c r="B67">
+        <v>110007</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" ht="15" spans="1:7">
+      <c r="A68">
+        <v>160063</v>
+      </c>
+      <c r="B68">
+        <v>110007</v>
+      </c>
+      <c r="C68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" t="s">
+        <v>98</v>
+      </c>
+      <c r="G68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" ht="15" spans="1:7">
+      <c r="A69">
+        <v>160064</v>
+      </c>
+      <c r="B69">
+        <v>110007</v>
+      </c>
+      <c r="C69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" ht="15" spans="1:7">
+      <c r="A70">
+        <v>160065</v>
+      </c>
+      <c r="B70">
+        <v>110007</v>
+      </c>
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>100</v>
+      </c>
+      <c r="F70" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" ht="15" spans="1:7">
+      <c r="A71">
+        <v>160066</v>
+      </c>
+      <c r="B71">
+        <v>110007</v>
+      </c>
+      <c r="C71" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+      <c r="E71" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" t="s">
+        <v>98</v>
+      </c>
+      <c r="G71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" ht="15" spans="1:7">
+      <c r="A72">
+        <v>160067</v>
+      </c>
+      <c r="B72">
+        <v>110007</v>
+      </c>
+      <c r="C72" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72">
+        <v>7</v>
+      </c>
+      <c r="E72" t="s">
+        <v>102</v>
+      </c>
+      <c r="F72" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" ht="15" spans="1:7">
+      <c r="A73">
+        <v>160068</v>
+      </c>
+      <c r="B73">
+        <v>110007</v>
+      </c>
+      <c r="C73" t="s">
+        <v>94</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>103</v>
+      </c>
+      <c r="F73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" ht="15" spans="1:7">
+      <c r="A74">
+        <v>160069</v>
+      </c>
+      <c r="B74">
+        <v>110007</v>
+      </c>
+      <c r="C74" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74">
+        <v>9</v>
+      </c>
+      <c r="E74" t="s">
+        <v>104</v>
+      </c>
+      <c r="F74" t="s">
+        <v>98</v>
+      </c>
+      <c r="G74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" ht="15" spans="1:7">
+      <c r="A75">
+        <v>160070</v>
+      </c>
+      <c r="B75">
+        <v>110007</v>
+      </c>
+      <c r="C75" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" t="s">
+        <v>24</v>
+      </c>
+      <c r="G75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" ht="15" spans="1:7">
+      <c r="A76">
+        <v>160071</v>
+      </c>
+      <c r="B76">
+        <v>110008</v>
+      </c>
+      <c r="C76" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" t="s">
+        <v>24</v>
+      </c>
+      <c r="G76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" ht="15" spans="1:7">
+      <c r="A77">
+        <v>160072</v>
+      </c>
+      <c r="B77">
+        <v>110008</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+      <c r="E77" t="s">
+        <v>108</v>
+      </c>
+      <c r="F77" t="s">
+        <v>24</v>
+      </c>
+      <c r="G77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" ht="15" spans="1:7">
+      <c r="A78">
+        <v>160073</v>
+      </c>
+      <c r="B78">
+        <v>110008</v>
+      </c>
+      <c r="C78" t="s">
+        <v>106</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>109</v>
+      </c>
+      <c r="F78" t="s">
+        <v>110</v>
+      </c>
+      <c r="G78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" ht="15" spans="1:7">
+      <c r="A79">
+        <v>160074</v>
+      </c>
+      <c r="B79">
+        <v>110008</v>
+      </c>
+      <c r="C79" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>111</v>
+      </c>
+      <c r="F79" t="s">
+        <v>24</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" ht="15" spans="1:7">
+      <c r="A80">
+        <v>160075</v>
+      </c>
+      <c r="B80">
+        <v>110008</v>
+      </c>
+      <c r="C80" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80" t="s">
+        <v>112</v>
+      </c>
+      <c r="F80" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" ht="15" spans="1:7">
+      <c r="A81">
+        <v>160076</v>
+      </c>
+      <c r="B81">
+        <v>110008</v>
+      </c>
+      <c r="C81" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+      <c r="E81" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" t="s">
+        <v>110</v>
+      </c>
+      <c r="G81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" ht="15" spans="1:7">
+      <c r="A82">
+        <v>160077</v>
+      </c>
+      <c r="B82">
+        <v>110008</v>
+      </c>
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82">
+        <v>7</v>
+      </c>
+      <c r="E82" t="s">
+        <v>114</v>
+      </c>
+      <c r="F82" t="s">
+        <v>24</v>
+      </c>
+      <c r="G82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" ht="15" spans="1:7">
+      <c r="A83">
+        <v>160078</v>
+      </c>
+      <c r="B83">
+        <v>110008</v>
+      </c>
+      <c r="C83" t="s">
+        <v>106</v>
+      </c>
+      <c r="D83">
+        <v>8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>115</v>
+      </c>
+      <c r="F83" t="s">
+        <v>24</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" ht="15" spans="1:7">
+      <c r="A84">
+        <v>160079</v>
+      </c>
+      <c r="B84">
+        <v>110008</v>
+      </c>
+      <c r="C84" t="s">
+        <v>106</v>
+      </c>
+      <c r="D84">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" t="s">
+        <v>110</v>
+      </c>
+      <c r="G84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" ht="15" spans="1:7">
+      <c r="A85">
+        <v>160080</v>
+      </c>
+      <c r="B85">
+        <v>110008</v>
+      </c>
+      <c r="C85" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85">
+        <v>10</v>
+      </c>
+      <c r="E85" t="s">
+        <v>117</v>
+      </c>
+      <c r="F85" t="s">
+        <v>24</v>
+      </c>
+      <c r="G85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" ht="15" spans="1:7">
+      <c r="A86">
+        <v>160081</v>
+      </c>
+      <c r="B86">
+        <v>110009</v>
+      </c>
+      <c r="C86" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>119</v>
+      </c>
+      <c r="F86" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" ht="15" spans="1:7">
+      <c r="A87">
+        <v>160082</v>
+      </c>
+      <c r="B87">
+        <v>110009</v>
+      </c>
+      <c r="C87" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87" t="s">
+        <v>120</v>
+      </c>
+      <c r="F87" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" ht="15" spans="1:7">
+      <c r="A88">
+        <v>160083</v>
+      </c>
+      <c r="B88">
+        <v>110009</v>
+      </c>
+      <c r="C88" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
+      </c>
+      <c r="E88" t="s">
+        <v>121</v>
+      </c>
+      <c r="F88" t="s">
+        <v>122</v>
+      </c>
+      <c r="G88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" ht="15" spans="1:7">
+      <c r="A89">
+        <v>160084</v>
+      </c>
+      <c r="B89">
+        <v>110009</v>
+      </c>
+      <c r="C89" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>123</v>
+      </c>
+      <c r="F89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" ht="15" spans="1:7">
+      <c r="A90">
+        <v>160085</v>
+      </c>
+      <c r="B90">
+        <v>110009</v>
+      </c>
+      <c r="C90" t="s">
+        <v>118</v>
+      </c>
+      <c r="D90">
+        <v>5</v>
+      </c>
+      <c r="E90" t="s">
+        <v>124</v>
+      </c>
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" ht="15" spans="1:7">
+      <c r="A91">
+        <v>160086</v>
+      </c>
+      <c r="B91">
+        <v>110009</v>
+      </c>
+      <c r="C91" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+      <c r="E91" t="s">
+        <v>125</v>
+      </c>
+      <c r="F91" t="s">
+        <v>122</v>
+      </c>
+      <c r="G91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" ht="15" spans="1:7">
+      <c r="A92">
+        <v>160087</v>
+      </c>
+      <c r="B92">
+        <v>110009</v>
+      </c>
+      <c r="C92" t="s">
+        <v>118</v>
+      </c>
+      <c r="D92">
+        <v>7</v>
+      </c>
+      <c r="E92" t="s">
+        <v>126</v>
+      </c>
+      <c r="F92" t="s">
+        <v>24</v>
+      </c>
+      <c r="G92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" ht="15" spans="1:7">
+      <c r="A93">
+        <v>160088</v>
+      </c>
+      <c r="B93">
+        <v>110009</v>
+      </c>
+      <c r="C93" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93">
+        <v>8</v>
+      </c>
+      <c r="E93" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" ht="15" spans="1:7">
+      <c r="A94">
+        <v>160089</v>
+      </c>
+      <c r="B94">
+        <v>110009</v>
+      </c>
+      <c r="C94" t="s">
+        <v>118</v>
+      </c>
+      <c r="D94">
+        <v>9</v>
+      </c>
+      <c r="E94" t="s">
+        <v>128</v>
+      </c>
+      <c r="F94" t="s">
+        <v>122</v>
+      </c>
+      <c r="G94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" ht="15" spans="1:7">
+      <c r="A95">
+        <v>160090</v>
+      </c>
+      <c r="B95">
+        <v>110009</v>
+      </c>
+      <c r="C95" t="s">
+        <v>118</v>
+      </c>
+      <c r="D95">
+        <v>10</v>
+      </c>
+      <c r="E95" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" t="s">
+        <v>24</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/策划/excel/16_RelmEvent.xlsx
+++ b/策划/excel/16_RelmEvent.xlsx
@@ -1,38 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\策划\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView windowWidth="27315" windowHeight="10470"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25935" windowHeight="15735"/>
   </bookViews>
   <sheets>
-    <sheet name="16_RelmEvent" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="16_RelmEvent" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="222">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -49,6 +31,9 @@
     <t>战斗事件池</t>
   </si>
   <si>
+    <t>未知事件池</t>
+  </si>
+  <si>
     <t>商店事件池</t>
   </si>
   <si>
@@ -70,6 +55,9 @@
     <t>fightPool</t>
   </si>
   <si>
+    <t>unknownEvent</t>
+  </si>
+  <si>
     <t>shopPool</t>
   </si>
   <si>
@@ -97,696 +85,630 @@
     <t>[150091]</t>
   </si>
   <si>
+    <t>[220001,220002]</t>
+  </si>
+  <si>
     <t>[140001]</t>
   </si>
   <si>
-    <t>[60002,60001]</t>
+    <t>[60002,60001,60003]</t>
   </si>
   <si>
     <t>[150092]</t>
   </si>
   <si>
+    <t>[220003,220004]</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>[60002]</t>
+    <t>[60002,60003]</t>
   </si>
   <si>
     <t>[150093]</t>
   </si>
   <si>
+    <t>[220001,220003]</t>
+  </si>
+  <si>
     <t>[150094]</t>
   </si>
   <si>
+    <t>[220003,220005]</t>
+  </si>
+  <si>
     <t>[150095]</t>
   </si>
   <si>
+    <t>[220001,220004]</t>
+  </si>
+  <si>
     <t>[150096]</t>
   </si>
   <si>
+    <t>[220003,220006]</t>
+  </si>
+  <si>
     <t>[150097]</t>
   </si>
   <si>
+    <t>[220001,220005]</t>
+  </si>
+  <si>
     <t>[150098]</t>
   </si>
   <si>
+    <t>[220003,220007]</t>
+  </si>
+  <si>
     <t>[150099]</t>
   </si>
   <si>
+    <t>[220001,220006]</t>
+  </si>
+  <si>
     <t>[150100]</t>
   </si>
   <si>
+    <t>[220003,220008]</t>
+  </si>
+  <si>
     <t>米德加德</t>
   </si>
   <si>
     <t>[150011]</t>
   </si>
   <si>
+    <t>[220001,220007]</t>
+  </si>
+  <si>
     <t>[150012]</t>
   </si>
   <si>
+    <t>[220003,220009]</t>
+  </si>
+  <si>
     <t>[150013]</t>
   </si>
   <si>
+    <t>[220001,220008]</t>
+  </si>
+  <si>
     <t>[140002,140010]</t>
   </si>
   <si>
     <t>[150014]</t>
   </si>
   <si>
+    <t>[220003,220010]</t>
+  </si>
+  <si>
     <t>[150015]</t>
   </si>
   <si>
+    <t>[220001,220009]</t>
+  </si>
+  <si>
     <t>[150016]</t>
   </si>
   <si>
+    <t>[220003,220011]</t>
+  </si>
+  <si>
     <t>[150017]</t>
   </si>
   <si>
+    <t>[220001,220010]</t>
+  </si>
+  <si>
     <t>[150018]</t>
   </si>
   <si>
+    <t>[220003,220012]</t>
+  </si>
+  <si>
     <t>[150019]</t>
   </si>
   <si>
+    <t>[220001,220011]</t>
+  </si>
+  <si>
     <t>[150020]</t>
   </si>
   <si>
+    <t>[220003,220013]</t>
+  </si>
+  <si>
     <t>华纳海姆</t>
   </si>
   <si>
     <t>[150021]</t>
   </si>
   <si>
+    <t>[220001,220012]</t>
+  </si>
+  <si>
     <t>[150022]</t>
   </si>
   <si>
+    <t>[220003,220014]</t>
+  </si>
+  <si>
     <t>[150023]</t>
   </si>
   <si>
+    <t>[220001,220013]</t>
+  </si>
+  <si>
     <t>[140003]</t>
   </si>
   <si>
     <t>[150024]</t>
   </si>
   <si>
+    <t>[220003,220015]</t>
+  </si>
+  <si>
     <t>[150025]</t>
   </si>
   <si>
+    <t>[220001,220014]</t>
+  </si>
+  <si>
     <t>[150026]</t>
   </si>
   <si>
+    <t>[220003,220016]</t>
+  </si>
+  <si>
     <t>[150027]</t>
   </si>
   <si>
+    <t>[220001,220015]</t>
+  </si>
+  <si>
     <t>[150028]</t>
   </si>
   <si>
+    <t>[220003,220017]</t>
+  </si>
+  <si>
     <t>[150029]</t>
   </si>
   <si>
+    <t>[220001,220016]</t>
+  </si>
+  <si>
     <t>[150030]</t>
   </si>
   <si>
+    <t>[220003,220018]</t>
+  </si>
+  <si>
     <t>亚尔夫海姆</t>
   </si>
   <si>
     <t>[150031]</t>
   </si>
   <si>
+    <t>[220001,220017]</t>
+  </si>
+  <si>
     <t>[150032]</t>
   </si>
   <si>
+    <t>[220003,220019]</t>
+  </si>
+  <si>
     <t>[150033]</t>
   </si>
   <si>
+    <t>[220001,220018]</t>
+  </si>
+  <si>
     <t>[140004]</t>
   </si>
   <si>
     <t>[150034]</t>
   </si>
   <si>
+    <t>[220003,220020]</t>
+  </si>
+  <si>
     <t>[150035]</t>
   </si>
   <si>
+    <t>[220001,220019]</t>
+  </si>
+  <si>
     <t>[150036]</t>
   </si>
   <si>
+    <t>[220003,220021]</t>
+  </si>
+  <si>
     <t>[150037]</t>
   </si>
   <si>
+    <t>[220001,220020]</t>
+  </si>
+  <si>
     <t>[150038]</t>
   </si>
   <si>
+    <t>[220003,220022]</t>
+  </si>
+  <si>
     <t>[150039]</t>
   </si>
   <si>
+    <t>[220001,220021]</t>
+  </si>
+  <si>
     <t>[150040]</t>
   </si>
   <si>
+    <t>[220003,220023]</t>
+  </si>
+  <si>
     <t>约顿海姆</t>
   </si>
   <si>
     <t>[150041]</t>
   </si>
   <si>
+    <t>[220001,220022]</t>
+  </si>
+  <si>
     <t>[150042]</t>
   </si>
   <si>
+    <t>[220003,220024]</t>
+  </si>
+  <si>
     <t>[150043]</t>
   </si>
   <si>
+    <t>[220001,220023]</t>
+  </si>
+  <si>
     <t>[140005]</t>
   </si>
   <si>
     <t>[150044]</t>
   </si>
   <si>
+    <t>[220003,220025]</t>
+  </si>
+  <si>
     <t>[150045]</t>
   </si>
   <si>
+    <t>[220001,220024]</t>
+  </si>
+  <si>
     <t>[150046]</t>
   </si>
   <si>
+    <t>[220003,220026]</t>
+  </si>
+  <si>
     <t>[150047]</t>
   </si>
   <si>
+    <t>[220001,220025]</t>
+  </si>
+  <si>
     <t>[150048]</t>
   </si>
   <si>
+    <t>[220003,220027]</t>
+  </si>
+  <si>
     <t>[150049]</t>
   </si>
   <si>
+    <t>[220001,220026]</t>
+  </si>
+  <si>
     <t>[150050]</t>
   </si>
   <si>
+    <t>[220003,220028]</t>
+  </si>
+  <si>
     <t>尼达维勒</t>
   </si>
   <si>
     <t>[150051]</t>
   </si>
   <si>
+    <t>[220001,220027]</t>
+  </si>
+  <si>
     <t>[150052]</t>
   </si>
   <si>
+    <t>[220003,220029]</t>
+  </si>
+  <si>
     <t>[150053]</t>
   </si>
   <si>
+    <t>[220001,220028]</t>
+  </si>
+  <si>
     <t>[140006]</t>
   </si>
   <si>
     <t>[150054]</t>
   </si>
   <si>
+    <t>[220003,220030]</t>
+  </si>
+  <si>
     <t>[150055]</t>
   </si>
   <si>
+    <t>[220001,220029]</t>
+  </si>
+  <si>
     <t>[150056]</t>
   </si>
   <si>
+    <t>[220003,220031]</t>
+  </si>
+  <si>
     <t>[150057]</t>
   </si>
   <si>
+    <t>[220001,220030]</t>
+  </si>
+  <si>
     <t>[150058]</t>
   </si>
   <si>
+    <t>[220003,220032]</t>
+  </si>
+  <si>
     <t>[150059]</t>
   </si>
   <si>
+    <t>[220001,220031]</t>
+  </si>
+  <si>
     <t>[150060]</t>
   </si>
   <si>
+    <t>[220003,220033]</t>
+  </si>
+  <si>
     <t>尼福尔海姆</t>
   </si>
   <si>
     <t>[150061]</t>
   </si>
   <si>
+    <t>[220001,220032]</t>
+  </si>
+  <si>
     <t>[150062]</t>
   </si>
   <si>
+    <t>[220003,220034]</t>
+  </si>
+  <si>
     <t>[150063]</t>
   </si>
   <si>
+    <t>[220001,220033]</t>
+  </si>
+  <si>
     <t>[140007]</t>
   </si>
   <si>
     <t>[150064]</t>
   </si>
   <si>
+    <t>[220003,220035]</t>
+  </si>
+  <si>
     <t>[150065]</t>
   </si>
   <si>
+    <t>[220001,220034]</t>
+  </si>
+  <si>
     <t>[150066]</t>
   </si>
   <si>
+    <t>[220003,220036]</t>
+  </si>
+  <si>
     <t>[150067]</t>
   </si>
   <si>
+    <t>[220001,220035]</t>
+  </si>
+  <si>
     <t>[150068]</t>
   </si>
   <si>
+    <t>[220003,220037]</t>
+  </si>
+  <si>
     <t>[150069]</t>
   </si>
   <si>
+    <t>[220001,220036]</t>
+  </si>
+  <si>
     <t>[150070]</t>
   </si>
   <si>
+    <t>[220003,220038]</t>
+  </si>
+  <si>
     <t>穆斯贝尔海姆</t>
   </si>
   <si>
     <t>[150071]</t>
   </si>
   <si>
+    <t>[220001,220037]</t>
+  </si>
+  <si>
     <t>[150072]</t>
   </si>
   <si>
+    <t>[220003,220039]</t>
+  </si>
+  <si>
     <t>[150073]</t>
   </si>
   <si>
+    <t>[220001,220038]</t>
+  </si>
+  <si>
     <t>[140008]</t>
   </si>
   <si>
     <t>[150074]</t>
   </si>
   <si>
+    <t>[220003,220040]</t>
+  </si>
+  <si>
     <t>[150075]</t>
   </si>
   <si>
+    <t>[220001,220039]</t>
+  </si>
+  <si>
     <t>[150076]</t>
   </si>
   <si>
+    <t>[220003,220041]</t>
+  </si>
+  <si>
     <t>[150077]</t>
   </si>
   <si>
+    <t>[220001,220040]</t>
+  </si>
+  <si>
     <t>[150078]</t>
   </si>
   <si>
+    <t>[220003,220042]</t>
+  </si>
+  <si>
     <t>[150079]</t>
   </si>
   <si>
+    <t>[220001,220041]</t>
+  </si>
+  <si>
     <t>[150080]</t>
   </si>
   <si>
+    <t>[220003,220043]</t>
+  </si>
+  <si>
     <t>赫尔海姆</t>
   </si>
   <si>
     <t>[150081]</t>
   </si>
   <si>
+    <t>[220001,220042]</t>
+  </si>
+  <si>
     <t>[150082]</t>
   </si>
   <si>
+    <t>[220003,220044]</t>
+  </si>
+  <si>
     <t>[150083]</t>
   </si>
   <si>
+    <t>[220001,220043]</t>
+  </si>
+  <si>
     <t>[140009]</t>
   </si>
   <si>
     <t>[150084]</t>
   </si>
   <si>
+    <t>[220003,220045]</t>
+  </si>
+  <si>
     <t>[150085]</t>
   </si>
   <si>
+    <t>[220001,220044]</t>
+  </si>
+  <si>
     <t>[150086]</t>
   </si>
   <si>
+    <t>[220003,220046]</t>
+  </si>
+  <si>
     <t>[150087]</t>
   </si>
   <si>
+    <t>[220001,220045]</t>
+  </si>
+  <si>
     <t>[150088]</t>
   </si>
   <si>
+    <t>[220003,220047]</t>
+  </si>
+  <si>
     <t>[150089]</t>
   </si>
   <si>
+    <t>[220001,220046]</t>
+  </si>
+  <si>
     <t>[150090]</t>
+  </si>
+  <si>
+    <t>[220003,220048]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -794,251 +716,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1046,61 +726,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1299,20 +935,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G95"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H95"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="7" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.752380952381" customWidth="1"/>
     <col min="2" max="2" width="25.1238095238095" customWidth="1"/>
     <col min="3" max="4" width="13.247619047619" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="13.247619047619" customWidth="1"/>
+    <col min="6" max="6" width="60.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="37.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:7">
+    <row r="1" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,100 +970,115 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:7">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>160001</v>
       </c>
@@ -1435,22 +1086,25 @@
         <v>110001</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>160002</v>
       </c>
@@ -1458,22 +1112,25 @@
         <v>110001</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>160003</v>
       </c>
@@ -1481,22 +1138,25 @@
         <v>110001</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>160004</v>
       </c>
@@ -1504,22 +1164,25 @@
         <v>110001</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>160005</v>
       </c>
@@ -1527,22 +1190,25 @@
         <v>110001</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>160006</v>
       </c>
@@ -1550,22 +1216,25 @@
         <v>110001</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>160007</v>
       </c>
@@ -1573,22 +1242,25 @@
         <v>110001</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>160008</v>
       </c>
@@ -1596,22 +1268,25 @@
         <v>110001</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>160009</v>
       </c>
@@ -1619,22 +1294,25 @@
         <v>110001</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>160010</v>
       </c>
@@ -1642,22 +1320,25 @@
         <v>110001</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>160011</v>
       </c>
@@ -1665,22 +1346,25 @@
         <v>110002</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>160012</v>
       </c>
@@ -1688,22 +1372,25 @@
         <v>110002</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>160013</v>
       </c>
@@ -1711,22 +1398,25 @@
         <v>110002</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>160014</v>
       </c>
@@ -1734,22 +1424,25 @@
         <v>110002</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>160015</v>
       </c>
@@ -1757,22 +1450,25 @@
         <v>110002</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>160016</v>
       </c>
@@ -1780,22 +1476,25 @@
         <v>110002</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>160017</v>
       </c>
@@ -1803,22 +1502,25 @@
         <v>110002</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>160018</v>
       </c>
@@ -1826,22 +1528,25 @@
         <v>110002</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>160019</v>
       </c>
@@ -1849,22 +1554,25 @@
         <v>110002</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>160020</v>
       </c>
@@ -1872,22 +1580,25 @@
         <v>110002</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>160021</v>
       </c>
@@ -1895,22 +1606,25 @@
         <v>110003</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>160022</v>
       </c>
@@ -1918,22 +1632,25 @@
         <v>110003</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>160023</v>
       </c>
@@ -1941,22 +1658,25 @@
         <v>110003</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>160024</v>
       </c>
@@ -1964,22 +1684,25 @@
         <v>110003</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>160025</v>
       </c>
@@ -1987,22 +1710,25 @@
         <v>110003</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>160026</v>
       </c>
@@ -2010,22 +1736,25 @@
         <v>110003</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>160027</v>
       </c>
@@ -2033,22 +1762,25 @@
         <v>110003</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>160028</v>
       </c>
@@ -2056,22 +1788,25 @@
         <v>110003</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>160029</v>
       </c>
@@ -2079,22 +1814,25 @@
         <v>110003</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D34">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:7">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>160030</v>
       </c>
@@ -2102,22 +1840,25 @@
         <v>110003</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D35">
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>160031</v>
       </c>
@@ -2125,22 +1866,25 @@
         <v>110004</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>160032</v>
       </c>
@@ -2148,22 +1892,25 @@
         <v>110004</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>160033</v>
       </c>
@@ -2171,22 +1918,25 @@
         <v>110004</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" ht="15" spans="1:7">
+        <v>97</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>160034</v>
       </c>
@@ -2194,22 +1944,25 @@
         <v>110004</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>160035</v>
       </c>
@@ -2217,22 +1970,25 @@
         <v>110004</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D40">
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>160036</v>
       </c>
@@ -2240,22 +1996,25 @@
         <v>110004</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:7">
+        <v>97</v>
+      </c>
+      <c r="H41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>160037</v>
       </c>
@@ -2263,22 +2022,25 @@
         <v>110004</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D42">
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>160038</v>
       </c>
@@ -2286,22 +2048,25 @@
         <v>110004</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D43">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>160039</v>
       </c>
@@ -2309,22 +2074,25 @@
         <v>110004</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D44">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:7">
+        <v>97</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>160040</v>
       </c>
@@ -2332,22 +2100,25 @@
         <v>110004</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>160041</v>
       </c>
@@ -2355,22 +2126,25 @@
         <v>110005</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>160042</v>
       </c>
@@ -2378,22 +2152,25 @@
         <v>110005</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>160043</v>
       </c>
@@ -2401,22 +2178,25 @@
         <v>110005</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" ht="15" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>160044</v>
       </c>
@@ -2424,22 +2204,25 @@
         <v>110005</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>160045</v>
       </c>
@@ -2447,22 +2230,25 @@
         <v>110005</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D50">
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>160046</v>
       </c>
@@ -2470,22 +2256,25 @@
         <v>110005</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D51">
         <v>6</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" ht="15" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>160047</v>
       </c>
@@ -2493,22 +2282,25 @@
         <v>110005</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D52">
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>160048</v>
       </c>
@@ -2516,22 +2308,25 @@
         <v>110005</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D53">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>160049</v>
       </c>
@@ -2539,22 +2334,25 @@
         <v>110005</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D54">
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" ht="15" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>160050</v>
       </c>
@@ -2562,22 +2360,25 @@
         <v>110005</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D55">
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>160051</v>
       </c>
@@ -2585,22 +2386,25 @@
         <v>110006</v>
       </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>160052</v>
       </c>
@@ -2608,22 +2412,25 @@
         <v>110006</v>
       </c>
       <c r="C57" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>160053</v>
       </c>
@@ -2631,22 +2438,25 @@
         <v>110006</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D58">
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="F58" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" ht="15" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>160054</v>
       </c>
@@ -2654,22 +2464,25 @@
         <v>110006</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H59" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>160055</v>
       </c>
@@ -2677,22 +2490,25 @@
         <v>110006</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D60">
         <v>5</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="G60" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H60" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>160056</v>
       </c>
@@ -2700,22 +2516,25 @@
         <v>110006</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D61">
         <v>6</v>
       </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="F61" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" ht="15" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>160057</v>
       </c>
@@ -2723,22 +2542,25 @@
         <v>110006</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D62">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>160058</v>
       </c>
@@ -2746,22 +2568,25 @@
         <v>110006</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D63">
         <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>160059</v>
       </c>
@@ -2769,22 +2594,25 @@
         <v>110006</v>
       </c>
       <c r="C64" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D64">
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="F64" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" ht="15" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>160060</v>
       </c>
@@ -2792,22 +2620,25 @@
         <v>110006</v>
       </c>
       <c r="C65" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D65">
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="F65" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>160061</v>
       </c>
@@ -2815,22 +2646,25 @@
         <v>110007</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="F66" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>160062</v>
       </c>
@@ -2838,22 +2672,25 @@
         <v>110007</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>160063</v>
       </c>
@@ -2861,22 +2698,25 @@
         <v>110007</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="F68" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" ht="15" spans="1:7">
+        <v>163</v>
+      </c>
+      <c r="H68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>160064</v>
       </c>
@@ -2884,22 +2724,25 @@
         <v>110007</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="70" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H69" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>160065</v>
       </c>
@@ -2907,22 +2750,25 @@
         <v>110007</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D70">
         <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>160066</v>
       </c>
@@ -2930,22 +2776,25 @@
         <v>110007</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D71">
         <v>6</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="F71" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" ht="15" spans="1:7">
+        <v>163</v>
+      </c>
+      <c r="H71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>160067</v>
       </c>
@@ -2953,22 +2802,25 @@
         <v>110007</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D72">
         <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H72" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>160068</v>
       </c>
@@ -2976,22 +2828,25 @@
         <v>110007</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D73">
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H73" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>160069</v>
       </c>
@@ -2999,22 +2854,25 @@
         <v>110007</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D74">
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="G74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" ht="15" spans="1:7">
+        <v>163</v>
+      </c>
+      <c r="H74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>160070</v>
       </c>
@@ -3022,22 +2880,25 @@
         <v>110007</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="D75">
         <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="G75" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H75" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>160071</v>
       </c>
@@ -3045,22 +2906,25 @@
         <v>110008</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>160072</v>
       </c>
@@ -3068,22 +2932,25 @@
         <v>110008</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>160073</v>
       </c>
@@ -3091,22 +2958,25 @@
         <v>110008</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="F78" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" ht="15" spans="1:7">
+        <v>185</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>160074</v>
       </c>
@@ -3114,22 +2984,25 @@
         <v>110008</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D79">
         <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>160075</v>
       </c>
@@ -3137,22 +3010,25 @@
         <v>110008</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D80">
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="F80" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>160076</v>
       </c>
@@ -3160,22 +3036,25 @@
         <v>110008</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D81">
         <v>6</v>
       </c>
       <c r="E81" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="G81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" ht="15" spans="1:7">
+        <v>185</v>
+      </c>
+      <c r="H81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>160077</v>
       </c>
@@ -3183,22 +3062,25 @@
         <v>110008</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D82">
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="F82" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H82" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>160078</v>
       </c>
@@ -3206,22 +3088,25 @@
         <v>110008</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D83">
         <v>8</v>
       </c>
       <c r="E83" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>195</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="84" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>160079</v>
       </c>
@@ -3229,22 +3114,25 @@
         <v>110008</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D84">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="F84" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="G84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" ht="15" spans="1:7">
+        <v>185</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>160080</v>
       </c>
@@ -3252,22 +3140,25 @@
         <v>110008</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D85">
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>160081</v>
       </c>
@@ -3275,22 +3166,25 @@
         <v>110009</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="F86" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="G86" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>160082</v>
       </c>
@@ -3298,22 +3192,25 @@
         <v>110009</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D87">
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="88" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>160083</v>
       </c>
@@ -3321,22 +3218,25 @@
         <v>110009</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D88">
         <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="F88" t="s">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="G88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" ht="15" spans="1:7">
+        <v>207</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>160084</v>
       </c>
@@ -3344,22 +3244,25 @@
         <v>110009</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D89">
         <v>4</v>
       </c>
       <c r="E89" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="90" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H89" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>160085</v>
       </c>
@@ -3367,22 +3270,25 @@
         <v>110009</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D90">
         <v>5</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="F90" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>160086</v>
       </c>
@@ -3390,22 +3296,25 @@
         <v>110009</v>
       </c>
       <c r="C91" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D91">
         <v>6</v>
       </c>
       <c r="E91" t="s">
-        <v>125</v>
+        <v>212</v>
       </c>
       <c r="F91" t="s">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="G91" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" ht="15" spans="1:7">
+        <v>207</v>
+      </c>
+      <c r="H91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>160087</v>
       </c>
@@ -3413,22 +3322,25 @@
         <v>110009</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D92">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H92" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>160088</v>
       </c>
@@ -3436,22 +3348,25 @@
         <v>110009</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D93">
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" ht="15" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>160089</v>
       </c>
@@ -3459,22 +3374,25 @@
         <v>110009</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D94">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="F94" t="s">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="G94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" ht="15" spans="1:7">
+        <v>207</v>
+      </c>
+      <c r="H94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>160090</v>
       </c>
@@ -3482,23 +3400,25 @@
         <v>110009</v>
       </c>
       <c r="C95" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="D95">
         <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="F95" t="s">
-        <v>24</v>
+        <v>221</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H95" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>